--- a/セリフ編集/その他セリフ/05-引退・引き抜き・引き留め.xlsx
+++ b/セリフ編集/その他セリフ/05-引退・引き抜き・引き留め.xlsx
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal._default[1]</t>
+          <t xml:space="preserve">A1_champion._default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -288,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.normal._default[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion._default.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -303,7 +303,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.normal._default[2]</t>
+          <t xml:space="preserve">A1_champion._default.normal[2]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="5">
@@ -320,7 +320,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion._default.bold[1]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold._default[1]</t>
+          <t xml:space="preserve">A1_champion._default.bold[1]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="6">
@@ -352,7 +352,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion._default.quiet[1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.quiet._default[1]</t>
+          <t xml:space="preserve">A1_champion._default.quiet[1]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="7">
@@ -384,7 +384,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.shy._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion._default.shy[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.shy._default[1]</t>
+          <t xml:space="preserve">A1_champion._default.shy[1]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="8">
@@ -416,7 +416,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing._default[1]</t>
+          <t xml:space="preserve">A1_champion._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="9">
@@ -448,7 +448,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.earnest._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion._default.earnest[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.earnest._default[1]</t>
+          <t xml:space="preserve">A1_champion._default.earnest[1]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="10">
@@ -480,7 +480,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.emotional._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion._default.emotional[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.emotional._default[1]</t>
+          <t xml:space="preserve">A1_champion._default.emotional[1]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="10">
@@ -512,7 +512,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned._default.normal[1]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal._default[1]</t>
+          <t xml:space="preserve">A2_uncrowned._default.normal[1]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="5">
@@ -544,7 +544,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.normal._default[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned._default.normal[2]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.normal._default[2]</t>
+          <t xml:space="preserve">A2_uncrowned._default.normal[2]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="5">
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned._default.bold[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold._default[1]</t>
+          <t xml:space="preserve">A2_uncrowned._default.bold[1]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="6">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned._default.quiet[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.quiet._default[1]</t>
+          <t xml:space="preserve">A2_uncrowned._default.quiet[1]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="7">
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.shy._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned._default.shy[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.shy._default[1]</t>
+          <t xml:space="preserve">A2_uncrowned._default.shy[1]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="8">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.easygoing._default[1]</t>
+          <t xml:space="preserve">A2_uncrowned._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="9">
@@ -704,7 +704,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.earnest._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned._default.earnest[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.earnest._default[1]</t>
+          <t xml:space="preserve">A2_uncrowned._default.earnest[1]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="10">
@@ -736,7 +736,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.emotional._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned._default.emotional[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.emotional._default[1]</t>
+          <t xml:space="preserve">A2_uncrowned._default.emotional[1]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="10">
@@ -768,7 +768,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel._default.normal[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal._default[1]</t>
+          <t xml:space="preserve">A3_heel._default.normal[1]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="5">
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.normal._default[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel._default.normal[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.normal._default[2]</t>
+          <t xml:space="preserve">A3_heel._default.normal[2]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="5">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel._default.bold[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold._default[1]</t>
+          <t xml:space="preserve">A3_heel._default.bold[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="6">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel._default.quiet[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.quiet._default[1]</t>
+          <t xml:space="preserve">A3_heel._default.quiet[1]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="7">
@@ -896,7 +896,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.shy._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel._default.shy[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.shy._default[1]</t>
+          <t xml:space="preserve">A3_heel._default.shy[1]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="8">
@@ -928,7 +928,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.easygoing._default[1]</t>
+          <t xml:space="preserve">A3_heel._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="9">
@@ -960,7 +960,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.earnest._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel._default.earnest[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.earnest._default[1]</t>
+          <t xml:space="preserve">A3_heel._default.earnest[1]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="10">
@@ -992,7 +992,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.emotional._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel._default.emotional[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.emotional._default[1]</t>
+          <t xml:space="preserve">A3_heel._default.emotional[1]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="10">
@@ -1024,7 +1024,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran._default.normal[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal._default[1]</t>
+          <t xml:space="preserve">A4_veteran._default.normal[1]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="5">
@@ -1056,7 +1056,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.normal._default[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran._default.normal[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.normal._default[2]</t>
+          <t xml:space="preserve">A4_veteran._default.normal[2]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="5">
@@ -1088,7 +1088,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran._default.bold[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold._default[1]</t>
+          <t xml:space="preserve">A4_veteran._default.bold[1]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="6">
@@ -1120,7 +1120,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran._default.quiet[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.quiet._default[1]</t>
+          <t xml:space="preserve">A4_veteran._default.quiet[1]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="7">
@@ -1152,7 +1152,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.shy._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran._default.shy[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.shy._default[1]</t>
+          <t xml:space="preserve">A4_veteran._default.shy[1]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="8">
@@ -1184,7 +1184,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.easygoing._default[1]</t>
+          <t xml:space="preserve">A4_veteran._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="9">
@@ -1216,7 +1216,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.earnest._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran._default.earnest[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.earnest._default[1]</t>
+          <t xml:space="preserve">A4_veteran._default.earnest[1]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="10">
@@ -1248,7 +1248,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.emotional._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran._default.emotional[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.emotional._default[1]</t>
+          <t xml:space="preserve">A4_veteran._default.emotional[1]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="10">
@@ -1280,7 +1280,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young._default.normal[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal._default[1]</t>
+          <t xml:space="preserve">B1_young._default.normal[1]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="5">
@@ -1312,7 +1312,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.normal._default[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young._default.normal[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.normal._default[2]</t>
+          <t xml:space="preserve">B1_young._default.normal[2]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="5">
@@ -1344,7 +1344,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young._default.bold[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold._default[1]</t>
+          <t xml:space="preserve">B1_young._default.bold[1]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="6">
@@ -1376,7 +1376,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young._default.quiet[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.quiet._default[1]</t>
+          <t xml:space="preserve">B1_young._default.quiet[1]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="7">
@@ -1408,7 +1408,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.shy._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young._default.shy[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.shy._default[1]</t>
+          <t xml:space="preserve">B1_young._default.shy[1]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="8">
@@ -1440,7 +1440,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.easygoing._default[1]</t>
+          <t xml:space="preserve">B1_young._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="9">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.earnest._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young._default.earnest[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.earnest._default[1]</t>
+          <t xml:space="preserve">B1_young._default.earnest[1]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="10">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.emotional._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young._default.emotional[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.emotional._default[1]</t>
+          <t xml:space="preserve">B1_young._default.emotional[1]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="10">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime._default.normal[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal._default[1]</t>
+          <t xml:space="preserve">B2_prime._default.normal[1]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="5">
@@ -1568,7 +1568,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.normal._default[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime._default.normal[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.normal._default[2]</t>
+          <t xml:space="preserve">B2_prime._default.normal[2]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="5">
@@ -1600,7 +1600,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime._default.bold[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold._default[1]</t>
+          <t xml:space="preserve">B2_prime._default.bold[1]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="6">
@@ -1632,7 +1632,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime._default.quiet[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.quiet._default[1]</t>
+          <t xml:space="preserve">B2_prime._default.quiet[1]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="7">
@@ -1664,7 +1664,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.shy._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime._default.shy[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.shy._default[1]</t>
+          <t xml:space="preserve">B2_prime._default.shy[1]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="8">
@@ -1696,7 +1696,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.easygoing._default[1]</t>
+          <t xml:space="preserve">B2_prime._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="9">
@@ -1728,7 +1728,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.earnest._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime._default.earnest[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.earnest._default[1]</t>
+          <t xml:space="preserve">B2_prime._default.earnest[1]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="10">
@@ -1760,7 +1760,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.emotional._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime._default.emotional[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.emotional._default[1]</t>
+          <t xml:space="preserve">B2_prime._default.emotional[1]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="10">
@@ -1792,7 +1792,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older._default.normal[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal._default[1]</t>
+          <t xml:space="preserve">B3_older._default.normal[1]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="5">
@@ -1824,7 +1824,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.normal._default[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older._default.normal[2]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.normal._default[2]</t>
+          <t xml:space="preserve">B3_older._default.normal[2]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="5">
@@ -1856,7 +1856,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older._default.bold[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold._default[1]</t>
+          <t xml:space="preserve">B3_older._default.bold[1]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="6">
@@ -1888,7 +1888,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older._default.quiet[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.quiet._default[1]</t>
+          <t xml:space="preserve">B3_older._default.quiet[1]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="7">
@@ -1920,7 +1920,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.shy._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older._default.shy[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.shy._default[1]</t>
+          <t xml:space="preserve">B3_older._default.shy[1]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="8">
@@ -1952,7 +1952,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.easygoing._default[1]</t>
+          <t xml:space="preserve">B3_older._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="9">
@@ -1984,7 +1984,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.earnest._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older._default.earnest[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.earnest._default[1]</t>
+          <t xml:space="preserve">B3_older._default.earnest[1]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="10">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.emotional._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older._default.emotional[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.emotional._default[1]</t>
+          <t xml:space="preserve">B3_older._default.emotional[1]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="10">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury._default.normal[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal._default[1]</t>
+          <t xml:space="preserve">B4_champion_injury._default.normal[1]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="5">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.normal._default[2]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury._default.normal[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.normal._default[2]</t>
+          <t xml:space="preserve">B4_champion_injury._default.normal[2]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="5">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury._default.bold[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold._default[1]</t>
+          <t xml:space="preserve">B4_champion_injury._default.bold[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="6">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury._default.quiet[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.quiet._default[1]</t>
+          <t xml:space="preserve">B4_champion_injury._default.quiet[1]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="7">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.shy._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury._default.shy[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.shy._default[1]</t>
+          <t xml:space="preserve">B4_champion_injury._default.shy[1]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="8">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.easygoing._default[1]</t>
+          <t xml:space="preserve">B4_champion_injury._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="9">
@@ -2240,7 +2240,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.earnest._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury._default.earnest[1]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.earnest._default[1]</t>
+          <t xml:space="preserve">B4_champion_injury._default.earnest[1]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="10">
@@ -2272,7 +2272,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.emotional._default[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury._default.emotional[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.emotional._default[1]</t>
+          <t xml:space="preserve">B4_champion_injury._default.emotional[1]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="10">
@@ -2838,7 +2838,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.normal[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal._default[1]</t>
+          <t xml:space="preserve">accepted._default.normal[1]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="5">
@@ -2870,7 +2870,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.normal._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.normal[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.normal._default[2]</t>
+          <t xml:space="preserve">accepted._default.normal[2]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="5">
@@ -2902,7 +2902,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.bold[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold._default[1]</t>
+          <t xml:space="preserve">accepted._default.bold[1]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="6">
@@ -2934,7 +2934,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.bold[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold._default[2]</t>
+          <t xml:space="preserve">accepted._default.bold[2]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="6">
@@ -2966,7 +2966,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.quiet[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.quiet._default[1]</t>
+          <t xml:space="preserve">accepted._default.quiet[1]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="7">
@@ -2998,7 +2998,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.quiet[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.quiet._default[2]</t>
+          <t xml:space="preserve">accepted._default.quiet[2]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="7">
@@ -3030,7 +3030,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.shy._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.shy[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.shy._default[1]</t>
+          <t xml:space="preserve">accepted._default.shy[1]</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="8">
@@ -3062,7 +3062,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.shy._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.shy[2]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.shy._default[2]</t>
+          <t xml:space="preserve">accepted._default.shy[2]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="8">
@@ -3094,7 +3094,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing._default[1]</t>
+          <t xml:space="preserve">accepted._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="9">
@@ -3126,7 +3126,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing._default[2]</t>
+          <t xml:space="preserve">accepted._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="9">
@@ -3158,7 +3158,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.earnest[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest._default[1]</t>
+          <t xml:space="preserve">accepted._default.earnest[1]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="10">
@@ -3190,7 +3190,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.earnest._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.earnest[2]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.earnest._default[2]</t>
+          <t xml:space="preserve">accepted._default.earnest[2]</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="10">
@@ -3222,7 +3222,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.emotional[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.emotional._default[1]</t>
+          <t xml:space="preserve">accepted._default.emotional[1]</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="10">
@@ -3254,7 +3254,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted._default.emotional[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.emotional._default[2]</t>
+          <t xml:space="preserve">accepted._default.emotional[2]</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="10">
@@ -3286,7 +3286,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.normal[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal._default[1]</t>
+          <t xml:space="preserve">defended._default.normal[1]</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="5">
@@ -3318,7 +3318,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.normal._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.normal[2]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.normal._default[2]</t>
+          <t xml:space="preserve">defended._default.normal[2]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="5">
@@ -3350,7 +3350,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.bold[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold._default[1]</t>
+          <t xml:space="preserve">defended._default.bold[1]</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="6">
@@ -3382,7 +3382,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.bold[2]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold._default[2]</t>
+          <t xml:space="preserve">defended._default.bold[2]</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="6">
@@ -3414,7 +3414,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.quiet[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.quiet._default[1]</t>
+          <t xml:space="preserve">defended._default.quiet[1]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="7">
@@ -3446,7 +3446,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.quiet[2]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.quiet._default[2]</t>
+          <t xml:space="preserve">defended._default.quiet[2]</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="7">
@@ -3478,7 +3478,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.shy._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.shy[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.shy._default[1]</t>
+          <t xml:space="preserve">defended._default.shy[1]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="8">
@@ -3510,7 +3510,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.shy._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.shy[2]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.shy._default[2]</t>
+          <t xml:space="preserve">defended._default.shy[2]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="8">
@@ -3542,7 +3542,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing._default[1]</t>
+          <t xml:space="preserve">defended._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="9">
@@ -3574,7 +3574,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing._default[2]</t>
+          <t xml:space="preserve">defended._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="9">
@@ -3606,7 +3606,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.earnest[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest._default[1]</t>
+          <t xml:space="preserve">defended._default.earnest[1]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="10">
@@ -3638,7 +3638,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.earnest._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.earnest[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.earnest._default[2]</t>
+          <t xml:space="preserve">defended._default.earnest[2]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="10">
@@ -3670,7 +3670,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.emotional[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.emotional._default[1]</t>
+          <t xml:space="preserve">defended._default.emotional[1]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="10">
@@ -3702,7 +3702,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended._default.emotional[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.emotional._default[2]</t>
+          <t xml:space="preserve">defended._default.emotional[2]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="10">
@@ -3734,7 +3734,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.normal[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal._default[1]</t>
+          <t xml:space="preserve">defense_failed._default.normal[1]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="5">
@@ -3766,7 +3766,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.normal._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.normal[2]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.normal._default[2]</t>
+          <t xml:space="preserve">defense_failed._default.normal[2]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="5">
@@ -3798,7 +3798,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold._default[1]</t>
+          <t xml:space="preserve">defense_failed._default.bold[1]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="6">
@@ -3830,7 +3830,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.bold[2]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold._default[2]</t>
+          <t xml:space="preserve">defense_failed._default.bold[2]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="6">
@@ -3862,7 +3862,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.quiet[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.quiet._default[1]</t>
+          <t xml:space="preserve">defense_failed._default.quiet[1]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="7">
@@ -3894,7 +3894,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.quiet[2]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.quiet._default[2]</t>
+          <t xml:space="preserve">defense_failed._default.quiet[2]</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="7">
@@ -3926,7 +3926,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.shy._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.shy[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.shy._default[1]</t>
+          <t xml:space="preserve">defense_failed._default.shy[1]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="8">
@@ -3958,7 +3958,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.shy._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.shy[2]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.shy._default[2]</t>
+          <t xml:space="preserve">defense_failed._default.shy[2]</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="8">
@@ -3990,7 +3990,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing._default[1]</t>
+          <t xml:space="preserve">defense_failed._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="9">
@@ -4022,7 +4022,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing._default[2]</t>
+          <t xml:space="preserve">defense_failed._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="9">
@@ -4054,7 +4054,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest._default[1]</t>
+          <t xml:space="preserve">defense_failed._default.earnest[1]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="10">
@@ -4086,7 +4086,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.earnest._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.earnest[2]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.earnest._default[2]</t>
+          <t xml:space="preserve">defense_failed._default.earnest[2]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="10">
@@ -4118,7 +4118,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional._default[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.emotional[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.emotional._default[1]</t>
+          <t xml:space="preserve">defense_failed._default.emotional[1]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="10">
@@ -4150,7 +4150,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional._default[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed._default.emotional[2]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.emotional._default[2]</t>
+          <t xml:space="preserve">defense_failed._default.emotional[2]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="10">
@@ -4182,7 +4182,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal._default.normal[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal._default[1]</t>
+          <t xml:space="preserve">accept_terminal._default.normal[1]</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="5">
@@ -4214,7 +4214,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal._default.normal[2]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.normal._default[2]</t>
+          <t xml:space="preserve">accept_terminal._default.normal[2]</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="5">
@@ -4246,7 +4246,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal._default.bold[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold._default[1]</t>
+          <t xml:space="preserve">accept_terminal._default.bold[1]</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="6">
@@ -4278,7 +4278,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal._default.quiet[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.quiet._default[1]</t>
+          <t xml:space="preserve">accept_terminal._default.quiet[1]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="7">
@@ -4310,7 +4310,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal._default.shy[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.shy._default[1]</t>
+          <t xml:space="preserve">accept_terminal._default.shy[1]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="8">
@@ -4342,7 +4342,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing._default[1]</t>
+          <t xml:space="preserve">accept_terminal._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="9">
@@ -4374,7 +4374,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal._default.earnest[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.earnest._default[1]</t>
+          <t xml:space="preserve">accept_terminal._default.earnest[1]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="10">
@@ -4406,7 +4406,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal._default.emotional[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.emotional._default[1]</t>
+          <t xml:space="preserve">accept_terminal._default.emotional[1]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="10">
@@ -4438,7 +4438,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless._default.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal._default[1]</t>
+          <t xml:space="preserve">accept_winless._default.normal[1]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="5">
@@ -4470,7 +4470,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless._default.normal[2]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.normal._default[2]</t>
+          <t xml:space="preserve">accept_winless._default.normal[2]</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="5">
@@ -4502,7 +4502,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless._default.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.bold._default[1]</t>
+          <t xml:space="preserve">accept_winless._default.bold[1]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="6">
@@ -4534,7 +4534,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless._default.quiet[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.quiet._default[1]</t>
+          <t xml:space="preserve">accept_winless._default.quiet[1]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="7">
@@ -4566,7 +4566,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless._default.shy[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.shy._default[1]</t>
+          <t xml:space="preserve">accept_winless._default.shy[1]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="8">
@@ -4598,7 +4598,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.easygoing._default[1]</t>
+          <t xml:space="preserve">accept_winless._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="9">
@@ -4630,7 +4630,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless._default.earnest[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.earnest._default[1]</t>
+          <t xml:space="preserve">accept_winless._default.earnest[1]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="10">
@@ -4662,7 +4662,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless._default.emotional[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.emotional._default[1]</t>
+          <t xml:space="preserve">accept_winless._default.emotional[1]</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="10">
@@ -4694,7 +4694,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel._default.normal[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal._default[1]</t>
+          <t xml:space="preserve">accept_heel._default.normal[1]</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="5">
@@ -4726,7 +4726,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel._default.normal[2]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.normal._default[2]</t>
+          <t xml:space="preserve">accept_heel._default.normal[2]</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="5">
@@ -4758,7 +4758,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel._default.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.bold._default[1]</t>
+          <t xml:space="preserve">accept_heel._default.bold[1]</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="6">
@@ -4790,7 +4790,7 @@
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel._default.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.quiet._default[1]</t>
+          <t xml:space="preserve">accept_heel._default.quiet[1]</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="7">
@@ -4822,7 +4822,7 @@
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel._default.shy[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.shy._default[1]</t>
+          <t xml:space="preserve">accept_heel._default.shy[1]</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="8">
@@ -4854,7 +4854,7 @@
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.easygoing._default[1]</t>
+          <t xml:space="preserve">accept_heel._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="9">
@@ -4886,7 +4886,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel._default.earnest[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.earnest._default[1]</t>
+          <t xml:space="preserve">accept_heel._default.earnest[1]</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="10">
@@ -4918,7 +4918,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel._default.emotional[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.emotional._default[1]</t>
+          <t xml:space="preserve">accept_heel._default.emotional[1]</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="10">
@@ -4950,7 +4950,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ._default.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal._default[1]</t>
+          <t xml:space="preserve">accept_former_champ._default.normal[1]</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="5">
@@ -4982,7 +4982,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ._default.normal[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.normal._default[2]</t>
+          <t xml:space="preserve">accept_former_champ._default.normal[2]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="5">
@@ -5014,7 +5014,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ._default.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.bold._default[1]</t>
+          <t xml:space="preserve">accept_former_champ._default.bold[1]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="6">
@@ -5046,7 +5046,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ._default.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.quiet._default[1]</t>
+          <t xml:space="preserve">accept_former_champ._default.quiet[1]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="7">
@@ -5078,7 +5078,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ._default.shy[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.shy._default[1]</t>
+          <t xml:space="preserve">accept_former_champ._default.shy[1]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="8">
@@ -5110,7 +5110,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.easygoing._default[1]</t>
+          <t xml:space="preserve">accept_former_champ._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="9">
@@ -5142,7 +5142,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ._default.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.earnest._default[1]</t>
+          <t xml:space="preserve">accept_former_champ._default.earnest[1]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="10">
@@ -5174,7 +5174,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ._default.emotional[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.emotional._default[1]</t>
+          <t xml:space="preserve">accept_former_champ._default.emotional[1]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="10">
@@ -5206,7 +5206,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title._default.normal[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal._default[1]</t>
+          <t xml:space="preserve">accept_no_title._default.normal[1]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="5">
@@ -5238,7 +5238,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title._default.normal[2]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.normal._default[2]</t>
+          <t xml:space="preserve">accept_no_title._default.normal[2]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="5">
@@ -5270,7 +5270,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title._default.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.bold._default[1]</t>
+          <t xml:space="preserve">accept_no_title._default.bold[1]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="6">
@@ -5302,7 +5302,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title._default.quiet[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.quiet._default[1]</t>
+          <t xml:space="preserve">accept_no_title._default.quiet[1]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="7">
@@ -5334,7 +5334,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title._default.shy[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.shy._default[1]</t>
+          <t xml:space="preserve">accept_no_title._default.shy[1]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="8">
@@ -5366,7 +5366,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.easygoing._default[1]</t>
+          <t xml:space="preserve">accept_no_title._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="9">
@@ -5398,7 +5398,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title._default.earnest[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.earnest._default[1]</t>
+          <t xml:space="preserve">accept_no_title._default.earnest[1]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="10">
@@ -5430,7 +5430,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title._default.emotional[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.emotional._default[1]</t>
+          <t xml:space="preserve">accept_no_title._default.emotional[1]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="10">
@@ -5462,7 +5462,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ._default.normal[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal._default[1]</t>
+          <t xml:space="preserve">refuse_champ._default.normal[1]</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="5">
@@ -5494,7 +5494,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ._default.normal[2]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.normal._default[2]</t>
+          <t xml:space="preserve">refuse_champ._default.normal[2]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="5">
@@ -5526,7 +5526,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ._default.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold._default[1]</t>
+          <t xml:space="preserve">refuse_champ._default.bold[1]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="6">
@@ -5558,7 +5558,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ._default.quiet[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.quiet._default[1]</t>
+          <t xml:space="preserve">refuse_champ._default.quiet[1]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="7">
@@ -5590,7 +5590,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ._default.shy[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.shy._default[1]</t>
+          <t xml:space="preserve">refuse_champ._default.shy[1]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="8">
@@ -5622,7 +5622,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing._default[1]</t>
+          <t xml:space="preserve">refuse_champ._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="9">
@@ -5654,7 +5654,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ._default.earnest[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.earnest._default[1]</t>
+          <t xml:space="preserve">refuse_champ._default.earnest[1]</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="10">
@@ -5686,7 +5686,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ._default.emotional[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.emotional._default[1]</t>
+          <t xml:space="preserve">refuse_champ._default.emotional[1]</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="10">
@@ -5718,7 +5718,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust._default.normal[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal._default[1]</t>
+          <t xml:space="preserve">refuse_distrust._default.normal[1]</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="5">
@@ -5750,7 +5750,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust._default.normal[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.normal._default[2]</t>
+          <t xml:space="preserve">refuse_distrust._default.normal[2]</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="5">
@@ -5782,7 +5782,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust._default.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.bold._default[1]</t>
+          <t xml:space="preserve">refuse_distrust._default.bold[1]</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="6">
@@ -5814,7 +5814,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust._default.quiet[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.quiet._default[1]</t>
+          <t xml:space="preserve">refuse_distrust._default.quiet[1]</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="7">
@@ -5846,7 +5846,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust._default.shy[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.shy._default[1]</t>
+          <t xml:space="preserve">refuse_distrust._default.shy[1]</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="8">
@@ -5878,7 +5878,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.easygoing._default[1]</t>
+          <t xml:space="preserve">refuse_distrust._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="9">
@@ -5910,7 +5910,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust._default.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.earnest._default[1]</t>
+          <t xml:space="preserve">refuse_distrust._default.earnest[1]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="10">
@@ -5942,7 +5942,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust._default.emotional[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.emotional._default[1]</t>
+          <t xml:space="preserve">refuse_distrust._default.emotional[1]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="10">
@@ -5974,7 +5974,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel._default.normal[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal._default[1]</t>
+          <t xml:space="preserve">refuse_heel._default.normal[1]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="5">
@@ -6006,7 +6006,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel._default.normal[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.normal._default[2]</t>
+          <t xml:space="preserve">refuse_heel._default.normal[2]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="5">
@@ -6038,7 +6038,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel._default.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.bold._default[1]</t>
+          <t xml:space="preserve">refuse_heel._default.bold[1]</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="6">
@@ -6070,7 +6070,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel._default.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.quiet._default[1]</t>
+          <t xml:space="preserve">refuse_heel._default.quiet[1]</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="7">
@@ -6102,7 +6102,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel._default.shy[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.shy._default[1]</t>
+          <t xml:space="preserve">refuse_heel._default.shy[1]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="8">
@@ -6134,7 +6134,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.easygoing._default[1]</t>
+          <t xml:space="preserve">refuse_heel._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="9">
@@ -6166,7 +6166,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel._default.earnest[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.earnest._default[1]</t>
+          <t xml:space="preserve">refuse_heel._default.earnest[1]</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="10">
@@ -6198,7 +6198,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel._default.emotional[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.emotional._default[1]</t>
+          <t xml:space="preserve">refuse_heel._default.emotional[1]</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="10">
@@ -6230,7 +6230,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting._default.normal[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal._default[1]</t>
+          <t xml:space="preserve">refuse_fighting._default.normal[1]</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="5">
@@ -6262,7 +6262,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.normal._default[2]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting._default.normal[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.normal._default[2]</t>
+          <t xml:space="preserve">refuse_fighting._default.normal[2]</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="5">
@@ -6294,7 +6294,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting._default.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.bold._default[1]</t>
+          <t xml:space="preserve">refuse_fighting._default.bold[1]</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="6">
@@ -6326,7 +6326,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.quiet._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting._default.quiet[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.quiet._default[1]</t>
+          <t xml:space="preserve">refuse_fighting._default.quiet[1]</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="7">
@@ -6358,7 +6358,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.shy._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting._default.shy[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.shy._default[1]</t>
+          <t xml:space="preserve">refuse_fighting._default.shy[1]</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="8">
@@ -6390,7 +6390,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.easygoing._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.easygoing._default[1]</t>
+          <t xml:space="preserve">refuse_fighting._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="9">
@@ -6422,7 +6422,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.earnest._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting._default.earnest[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.earnest._default[1]</t>
+          <t xml:space="preserve">refuse_fighting._default.earnest[1]</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="10">
@@ -6454,7 +6454,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.emotional._default[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting._default.emotional[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.emotional._default[1]</t>
+          <t xml:space="preserve">refuse_fighting._default.emotional[1]</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="10">
@@ -6486,7 +6486,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.normal._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ._default.normal[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.normal._default[1]</t>
+          <t xml:space="preserve">former_champ._default.normal[1]</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="5">
@@ -6518,7 +6518,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ._default.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold._default[1]</t>
+          <t xml:space="preserve">former_champ._default.bold[1]</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="6">
@@ -6550,7 +6550,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ._default.quiet[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.quiet._default[1]</t>
+          <t xml:space="preserve">former_champ._default.quiet[1]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="7">
@@ -6582,7 +6582,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.shy._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ._default.shy[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.shy._default[1]</t>
+          <t xml:space="preserve">former_champ._default.shy[1]</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="8">
@@ -6614,7 +6614,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing._default[1]</t>
+          <t xml:space="preserve">former_champ._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="9">
@@ -6646,7 +6646,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.earnest._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ._default.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.earnest._default[1]</t>
+          <t xml:space="preserve">former_champ._default.earnest[1]</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="10">
@@ -6678,7 +6678,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.emotional._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ._default.emotional[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.emotional._default[1]</t>
+          <t xml:space="preserve">former_champ._default.emotional[1]</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="10">
@@ -6710,7 +6710,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.normal._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust._default.normal[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.normal._default[1]</t>
+          <t xml:space="preserve">high_trust._default.normal[1]</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="5">
@@ -6742,7 +6742,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.bold._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust._default.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.bold._default[1]</t>
+          <t xml:space="preserve">high_trust._default.bold[1]</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="6">
@@ -6774,7 +6774,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.quiet._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust._default.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.quiet._default[1]</t>
+          <t xml:space="preserve">high_trust._default.quiet[1]</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="7">
@@ -6806,7 +6806,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.shy._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust._default.shy[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.shy._default[1]</t>
+          <t xml:space="preserve">high_trust._default.shy[1]</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="8">
@@ -6838,7 +6838,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.easygoing._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.easygoing._default[1]</t>
+          <t xml:space="preserve">high_trust._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="9">
@@ -6870,7 +6870,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.earnest._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust._default.earnest[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.earnest._default[1]</t>
+          <t xml:space="preserve">high_trust._default.earnest[1]</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="10">
@@ -6902,7 +6902,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.emotional._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust._default.emotional[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.emotional._default[1]</t>
+          <t xml:space="preserve">high_trust._default.emotional[1]</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="10">
@@ -6934,7 +6934,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.normal._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel._default.normal[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.normal._default[1]</t>
+          <t xml:space="preserve">heel._default.normal[1]</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="5">
@@ -6966,7 +6966,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.bold._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel._default.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.bold._default[1]</t>
+          <t xml:space="preserve">heel._default.bold[1]</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="6">
@@ -6998,7 +6998,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.quiet._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel._default.quiet[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.quiet._default[1]</t>
+          <t xml:space="preserve">heel._default.quiet[1]</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="7">
@@ -7030,7 +7030,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.shy._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel._default.shy[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.shy._default[1]</t>
+          <t xml:space="preserve">heel._default.shy[1]</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="8">
@@ -7062,7 +7062,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.easygoing._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.easygoing._default[1]</t>
+          <t xml:space="preserve">heel._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="9">
@@ -7094,7 +7094,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.earnest._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel._default.earnest[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.earnest._default[1]</t>
+          <t xml:space="preserve">heel._default.earnest[1]</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="10">
@@ -7126,7 +7126,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.emotional._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel._default.emotional[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.emotional._default[1]</t>
+          <t xml:space="preserve">heel._default.emotional[1]</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="10">
@@ -7158,7 +7158,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default._default.normal[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal._default[1]</t>
+          <t xml:space="preserve">default._default.normal[1]</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="5">
@@ -7190,7 +7190,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.normal._default[2]</t>
+          <t xml:space="preserve">RETAIN_LINES.default._default.normal[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.normal._default[2]</t>
+          <t xml:space="preserve">default._default.normal[2]</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="5">
@@ -7222,7 +7222,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.bold._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default._default.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.bold._default[1]</t>
+          <t xml:space="preserve">default._default.bold[1]</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="6">
@@ -7254,7 +7254,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.quiet._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default._default.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.quiet._default[1]</t>
+          <t xml:space="preserve">default._default.quiet[1]</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="7">
@@ -7286,7 +7286,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.shy._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default._default.shy[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.shy._default[1]</t>
+          <t xml:space="preserve">default._default.shy[1]</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="8">
@@ -7318,7 +7318,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.easygoing._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.easygoing._default[1]</t>
+          <t xml:space="preserve">default._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="9">
@@ -7350,7 +7350,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.earnest._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default._default.earnest[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.earnest._default[1]</t>
+          <t xml:space="preserve">default._default.earnest[1]</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="10">
@@ -7382,7 +7382,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.emotional._default[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default._default.emotional[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.emotional._default[1]</t>
+          <t xml:space="preserve">default._default.emotional[1]</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="10">
@@ -7414,7 +7414,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.normal._default[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="5">
@@ -7446,7 +7446,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold._default[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="6">
@@ -7478,7 +7478,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="7">
@@ -7510,7 +7510,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.shy._default[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="8">
@@ -7542,7 +7542,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="9">
@@ -7574,7 +7574,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="10">
@@ -7606,7 +7606,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="10">
